--- a/data/trans_dic/P36B06_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,4; 79,61</t>
+          <t>73,97; 79,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,91; 89,26</t>
+          <t>84,8; 89,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,02; 88,03</t>
+          <t>83,15; 88,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,52; 85,46</t>
+          <t>81,41; 85,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,0; 92,33</t>
+          <t>89,02; 92,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,44; 90,58</t>
+          <t>86,26; 90,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,77; 82,23</t>
+          <t>78,75; 81,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,82; 90,37</t>
+          <t>87,9; 90,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85,79; 88,92</t>
+          <t>85,72; 88,88</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>73,38; 77,62</t>
+          <t>73,51; 77,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,71; 83,09</t>
+          <t>79,8; 83,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,57; 79,24</t>
+          <t>75,43; 79,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,33; 81,47</t>
+          <t>77,24; 81,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,55; 86,23</t>
+          <t>82,83; 86,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,09; 82,63</t>
+          <t>79,01; 82,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,12; 78,92</t>
+          <t>76,03; 78,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,75; 84,44</t>
+          <t>81,76; 84,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>77,81; 80,39</t>
+          <t>77,72; 80,31</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,12; 80,52</t>
+          <t>73,39; 80,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,14; 86,61</t>
+          <t>79,69; 86,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,08; 85,61</t>
+          <t>78,44; 85,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,82; 86,79</t>
+          <t>79,92; 86,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,03; 93,28</t>
+          <t>87,48; 93,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,15; 85,8</t>
+          <t>78,76; 85,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,44; 82,45</t>
+          <t>77,66; 82,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,28; 88,88</t>
+          <t>84,12; 89,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80,21; 84,7</t>
+          <t>80,14; 84,82</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,82; 77,73</t>
+          <t>74,89; 77,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,14; 84,64</t>
+          <t>81,96; 84,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,43; 81,35</t>
+          <t>78,52; 81,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,24; 82,89</t>
+          <t>80,35; 82,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,56; 88,83</t>
+          <t>86,5; 88,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,03; 84,61</t>
+          <t>82,05; 84,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,85; 80,03</t>
+          <t>77,96; 80,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,73; 86,51</t>
+          <t>84,71; 86,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>80,65; 82,59</t>
+          <t>80,73; 82,61</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>766787; 820509</t>
+          <t>762408; 816463</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>824953; 867263</t>
+          <t>823867; 865523</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>622941; 660518</t>
+          <t>623933; 662007</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1071270; 1123048</t>
+          <t>1069887; 1121385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1189661; 1234238</t>
+          <t>1189882; 1234341</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>858843; 899953</t>
+          <t>857040; 899418</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1847085; 1928163</t>
+          <t>1846571; 1921854</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2027034; 2086090</t>
+          <t>2028945; 2086447</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1496181; 1550722</t>
+          <t>1494896; 1550059</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1241326; 1312937</t>
+          <t>1243452; 1315902</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1564744; 1630990</t>
+          <t>1566560; 1634359</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1566956; 1643036</t>
+          <t>1564044; 1642352</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1226853; 1292641</t>
+          <t>1225449; 1290960</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1445900; 1510321</t>
+          <t>1450868; 1513944</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1568691; 1638992</t>
+          <t>1567276; 1642927</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2495291; 2587104</t>
+          <t>2492480; 2586046</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3036522; 3136404</t>
+          <t>3037106; 3133172</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3156666; 3261407</t>
+          <t>3153349; 3258145</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>403198; 443979</t>
+          <t>404700; 444681</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>379960; 415856</t>
+          <t>382629; 415600</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>432454; 468207</t>
+          <t>428961; 467597</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>380287; 413494</t>
+          <t>380759; 412766</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>399154; 427792</t>
+          <t>401195; 427427</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>434634; 471180</t>
+          <t>432488; 469785</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>795912; 847445</t>
+          <t>798246; 848366</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>791189; 834423</t>
+          <t>789682; 835562</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>879144; 928309</t>
+          <t>878369; 929610</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2449382; 2544630</t>
+          <t>2451498; 2550722</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2804762; 2890113</t>
+          <t>2798546; 2891720</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2643871; 2742288</t>
+          <t>2646854; 2744672</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2709677; 2799375</t>
+          <t>2713392; 2798214</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3070173; 3150858</t>
+          <t>3068039; 3151164</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2892536; 2983706</t>
+          <t>2893217; 2979782</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5177785; 5322608</t>
+          <t>5185270; 5322071</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5898595; 6022353</t>
+          <t>5897233; 6017569</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5562503; 5696296</t>
+          <t>5568186; 5697827</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B06_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,97; 79,22</t>
+          <t>74,3; 79,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,8; 89,08</t>
+          <t>85,26; 89,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,15; 88,23</t>
+          <t>82,97; 88,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,41; 85,33</t>
+          <t>81,26; 85,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,02; 92,34</t>
+          <t>88,92; 92,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,26; 90,52</t>
+          <t>86,38; 90,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,75; 81,96</t>
+          <t>78,71; 82,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,9; 90,39</t>
+          <t>88,0; 90,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85,72; 88,88</t>
+          <t>85,75; 89,03</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>73,51; 77,79</t>
+          <t>73,56; 77,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,8; 83,26</t>
+          <t>79,71; 83,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,43; 79,2</t>
+          <t>75,63; 79,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,24; 81,37</t>
+          <t>77,46; 81,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,83; 86,43</t>
+          <t>82,8; 86,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,01; 82,83</t>
+          <t>79,07; 82,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,03; 78,89</t>
+          <t>75,9; 79,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,76; 84,35</t>
+          <t>81,8; 84,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>77,72; 80,31</t>
+          <t>77,8; 80,37</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,39; 80,64</t>
+          <t>72,97; 80,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,69; 86,56</t>
+          <t>79,18; 86,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,44; 85,5</t>
+          <t>78,77; 85,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79,92; 86,64</t>
+          <t>80,19; 86,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,48; 93,2</t>
+          <t>87,14; 93,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,76; 85,55</t>
+          <t>79,11; 85,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,66; 82,54</t>
+          <t>77,61; 82,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,12; 89,01</t>
+          <t>84,16; 88,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80,14; 84,82</t>
+          <t>79,93; 84,63</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,89; 77,92</t>
+          <t>74,74; 77,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,96; 84,68</t>
+          <t>82,14; 84,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,52; 81,42</t>
+          <t>78,61; 81,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,35; 82,86</t>
+          <t>80,33; 82,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,5; 88,84</t>
+          <t>86,52; 88,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,05; 84,5</t>
+          <t>82,17; 84,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,96; 80,02</t>
+          <t>78,01; 79,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,71; 86,44</t>
+          <t>84,71; 86,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>80,73; 82,61</t>
+          <t>80,8; 82,59</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>762408; 816463</t>
+          <t>765786; 819228</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>823867; 865523</t>
+          <t>828406; 866860</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>623933; 662007</t>
+          <t>622573; 660742</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1069887; 1121385</t>
+          <t>1067803; 1121782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1189882; 1234341</t>
+          <t>1188547; 1234400</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>857040; 899418</t>
+          <t>858218; 901901</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1846571; 1921854</t>
+          <t>1845504; 1925590</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2028945; 2086447</t>
+          <t>2031360; 2090379</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1494896; 1550059</t>
+          <t>1495452; 1552563</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1243452; 1315902</t>
+          <t>1244382; 1315340</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1566560; 1634359</t>
+          <t>1564626; 1635562</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1564044; 1642352</t>
+          <t>1568250; 1644189</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1225449; 1290960</t>
+          <t>1228979; 1291892</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1450868; 1513944</t>
+          <t>1450365; 1512785</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1567276; 1642927</t>
+          <t>1568344; 1640712</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2492480; 2586046</t>
+          <t>2488209; 2589871</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3037106; 3133172</t>
+          <t>3038425; 3133809</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3153349; 3258145</t>
+          <t>3156267; 3260810</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>404700; 444681</t>
+          <t>402369; 445146</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>382629; 415600</t>
+          <t>380173; 414982</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>428961; 467597</t>
+          <t>430776; 468416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>380759; 412766</t>
+          <t>382013; 414221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>401195; 427427</t>
+          <t>399641; 428091</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>432488; 469785</t>
+          <t>434434; 470191</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>798246; 848366</t>
+          <t>797676; 851487</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>789682; 835562</t>
+          <t>790038; 834827</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>878369; 929610</t>
+          <t>876002; 927528</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2451498; 2550722</t>
+          <t>2446669; 2543041</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2798546; 2891720</t>
+          <t>2804839; 2895186</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2646854; 2744672</t>
+          <t>2649635; 2744884</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2713392; 2798214</t>
+          <t>2712791; 2798060</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3068039; 3151164</t>
+          <t>3068822; 3148300</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2893217; 2979782</t>
+          <t>2897606; 2983276</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5185270; 5322071</t>
+          <t>5188156; 5314879</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5897233; 6017569</t>
+          <t>5896888; 6019294</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5568186; 5697827</t>
+          <t>5572723; 5696250</t>
         </is>
       </c>
     </row>
